--- a/artfynd/A 20572-2025 artfynd.xlsx
+++ b/artfynd/A 20572-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,6 +920,127 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125051977</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57510</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Österrå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>607686</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7022768</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20572-2025 artfynd.xlsx
+++ b/artfynd/A 20572-2025 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>125051977</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>57624</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 20572-2025 artfynd.xlsx
+++ b/artfynd/A 20572-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -925,12 +925,7 @@
         <v>125051977</v>
       </c>
       <c r="B4" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57639</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,6 +1035,112 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125807038</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Österrå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>607686</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7022768</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20572-2025 artfynd.xlsx
+++ b/artfynd/A 20572-2025 artfynd.xlsx
@@ -1041,7 +1041,7 @@
         <v>125807038</v>
       </c>
       <c r="B5" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20572-2025 artfynd.xlsx
+++ b/artfynd/A 20572-2025 artfynd.xlsx
@@ -1041,7 +1041,7 @@
         <v>125807038</v>
       </c>
       <c r="B5" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20572-2025 artfynd.xlsx
+++ b/artfynd/A 20572-2025 artfynd.xlsx
@@ -1041,7 +1041,7 @@
         <v>125807038</v>
       </c>
       <c r="B5" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20572-2025 artfynd.xlsx
+++ b/artfynd/A 20572-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115813294</v>
+        <v>116532520</v>
       </c>
       <c r="B2" t="n">
-        <v>56323</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100045</v>
+        <v>100034</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,47 +796,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116532520</v>
+        <v>115813294</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100034</v>
+        <v>100045</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå kärrhök</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Circus cyaneus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -880,22 +870,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125051977</v>
+        <v>115919297</v>
       </c>
       <c r="B4" t="n">
-        <v>57639</v>
+        <v>56925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,43 +923,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102119</v>
+        <v>100045</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Österrå, Sollefteå, Ång</t>
+          <t>Österrå,  Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607686</v>
+        <v>607564</v>
       </c>
       <c r="R4" t="n">
-        <v>7022768</v>
+        <v>7022820</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,22 +986,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,11 +1031,11 @@
         <v>125807038</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1141,6 +1131,347 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125051977</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57942</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Österrå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>607686</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7022768</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>109008901</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58541</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102987</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sädesärla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Motacilla alba</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Österrå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>607593</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7022807</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>94312734</v>
+      </c>
+      <c r="B8" t="n">
+        <v>41972</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>213797</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Humlerotfjäril</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepialus humuli</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Österrå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>607602</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7022863</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20572-2025 artfynd.xlsx
+++ b/artfynd/A 20572-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116532520</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115813294</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115919297</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807038</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125051977</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1354,6 +1384,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109008901</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1472,8 +1507,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94312734</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 20572-2025 artfynd.xlsx
+++ b/artfynd/A 20572-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,32 +1159,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125051977</v>
+        <v>135914775</v>
       </c>
       <c r="B6" t="n">
-        <v>57942</v>
+        <v>57977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102119</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Österrå, Sollefteå, Ång</t>
+          <t>Österrå , Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607686</v>
+        <v>607597</v>
       </c>
       <c r="R6" t="n">
-        <v>7022768</v>
+        <v>7022862</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1233,22 +1233,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,16 +1274,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125051977</t>
+          <t>https://artportalen.se/Sighting/135914775</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109008901</v>
+        <v>125051977</v>
       </c>
       <c r="B7" t="n">
-        <v>58541</v>
+        <v>57942</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,16 +1291,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102987</v>
+        <v>102119</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1313,10 +1313,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1325,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607593</v>
+        <v>607686</v>
       </c>
       <c r="R7" t="n">
-        <v>7022807</v>
+        <v>7022768</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,12 +1354,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,16 +1395,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109008901</t>
+          <t>https://artportalen.se/Sighting/125051977</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94312734</v>
+        <v>109008901</v>
       </c>
       <c r="B8" t="n">
-        <v>41972</v>
+        <v>58541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,21 +1412,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>213797</v>
+        <v>102987</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Humlerotfjäril</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepialus humuli</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1425,23 +1434,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Österrå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607602</v>
+        <v>607593</v>
       </c>
       <c r="R8" t="n">
-        <v>7022863</v>
+        <v>7022807</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1468,22 +1476,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18:35</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18:35</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,6 +1506,129 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109008901</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>94312734</v>
+      </c>
+      <c r="B9" t="n">
+        <v>41972</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>213797</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Humlerotfjäril</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepialus humuli</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Österrå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>607602</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7022863</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/94312734</t>
         </is>
@@ -1522,6 +1643,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20572-2025 artfynd.xlsx
+++ b/artfynd/A 20572-2025 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>135914775</v>
       </c>
       <c r="B6" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 20572-2025 artfynd.xlsx
+++ b/artfynd/A 20572-2025 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>135914775</v>
       </c>
       <c r="B6" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 20572-2025 artfynd.xlsx
+++ b/artfynd/A 20572-2025 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>135914775</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 20572-2025 artfynd.xlsx
+++ b/artfynd/A 20572-2025 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>135914775</v>
       </c>
       <c r="B6" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 20572-2025 artfynd.xlsx
+++ b/artfynd/A 20572-2025 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>135914775</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 20572-2025 artfynd.xlsx
+++ b/artfynd/A 20572-2025 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>135914775</v>
       </c>
       <c r="B6" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
